--- a/Result/profitability/1909.xlsx
+++ b/Result/profitability/1909.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0825</v>
+        <v>-0.03125</v>
       </c>
       <c r="N2" t="n">
-        <v>9.77125</v>
+        <v>10.06125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.29</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02125</v>
+        <v>0.02749999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>10.68625</v>
+        <v>11.06875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00874999999999999</v>
+        <v>0.04749999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.27375</v>
+        <v>11.39625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03375000000000001</v>
+        <v>0.03375</v>
       </c>
       <c r="N5" t="n">
-        <v>8.998749999999999</v>
+        <v>9.3575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.002500000000000007</v>
+        <v>0.03749999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>9.866250000000001</v>
+        <v>10.27375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007499999999999993</v>
+        <v>0.015</v>
       </c>
       <c r="N7" t="n">
-        <v>10.8775</v>
+        <v>10.7325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01124999999999999</v>
+        <v>0.03999999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>10.96625</v>
+        <v>11.09</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.003750000000000009</v>
+        <v>-0.003750000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>10.63625</v>
@@ -1645,7 +1645,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01125000000000001</v>
+        <v>-0.01125</v>
       </c>
       <c r="N10" t="n">
         <v>10.675</v>
@@ -1772,7 +1772,7 @@
         <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03250000000000001</v>
+        <v>-0.0325</v>
       </c>
       <c r="N11" t="n">
         <v>9.966249999999999</v>
@@ -1899,7 +1899,7 @@
         <v>0.49</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02124999999999999</v>
+        <v>0.02125</v>
       </c>
       <c r="N12" t="n">
         <v>10.24125</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13487</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11964</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1524</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>216</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>111</v>
+      </c>
+      <c r="J75" t="n">
+        <v>327</v>
+      </c>
+      <c r="K75" t="n">
+        <v>270</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07250000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9900000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09602327837051416</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.636363636363636</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.870000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3404507710557534</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
